--- a/hall/resources/sample/ResearchInstitute.xlsx
+++ b/hall/resources/sample/ResearchInstitute.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
   <si>
     <t>id</t>
   </si>
@@ -43,16 +43,13 @@
     <t>游戏名称</t>
   </si>
   <si>
-    <t>组别</t>
-  </si>
-  <si>
     <t>属性技能位置坐标</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>Map&lt;int{_}int&gt;{|}</t>
+    <t>string</t>
   </si>
   <si>
     <t>level</t>
@@ -61,55 +58,121 @@
     <t>gameType</t>
   </si>
   <si>
-    <t>team</t>
-  </si>
-  <si>
     <t>location</t>
   </si>
   <si>
+    <t>client</t>
+  </si>
+  <si>
     <t>超级明星</t>
   </si>
   <si>
-    <t>0_0</t>
-  </si>
-  <si>
-    <t>0_1|1_1|2_1</t>
-  </si>
-  <si>
-    <t>0_2</t>
-  </si>
-  <si>
-    <t>0_3</t>
+    <t>10030001,0_0</t>
+  </si>
+  <si>
+    <t>10030002,0_1|10030003,1_1|10030004,2_1</t>
+  </si>
+  <si>
+    <t>10030005,0_2</t>
+  </si>
+  <si>
+    <t>10030006,0_3</t>
+  </si>
+  <si>
+    <t>10030007,0_3|10030008,1_3</t>
   </si>
   <si>
     <t>神马飞扬</t>
   </si>
   <si>
-    <t>0_1|1_1|2_1|3_1</t>
-  </si>
-  <si>
-    <t>0_2|1_2|2_2</t>
+    <t>10340001,0_0</t>
+  </si>
+  <si>
+    <t>10340002,0_1|10340003,1_1|10340004,2_1|10340005,3_1</t>
+  </si>
+  <si>
+    <t>10340006,0_2|10340007,1_2|10340008,2_2</t>
+  </si>
+  <si>
+    <t>10340009,0_3</t>
+  </si>
+  <si>
+    <t>10340010,0_4|10340011,1_4</t>
   </si>
   <si>
     <t>金蛇招财</t>
   </si>
   <si>
+    <t>10350001,0_0</t>
+  </si>
+  <si>
+    <t>10350002,0_1|10350003,1_1|10350004,2_1|10350005,3_1</t>
+  </si>
+  <si>
+    <t>10350006,0_2|10350007,1_2|10350008,2_2</t>
+  </si>
+  <si>
+    <t>10350009,0_3</t>
+  </si>
+  <si>
+    <t>10350010,0_4|10350011,1_4</t>
+  </si>
+  <si>
     <t>圣诞狂欢夜</t>
   </si>
   <si>
-    <t>0_2|1_2|2_2|3_2</t>
+    <t>10170001,0_0</t>
+  </si>
+  <si>
+    <t>10170002,0_1|10170003,1_1|10170004,2_1|10170005,3_1</t>
+  </si>
+  <si>
+    <t>10170006,0_2|1017007,1_2|10170008,2_2|10170009,3_2</t>
+  </si>
+  <si>
+    <t>10170010,0_3</t>
+  </si>
+  <si>
+    <t>10170011,0_4|10170011,1_4</t>
   </si>
   <si>
     <t>篮球巨星</t>
   </si>
   <si>
+    <t>10180001,0_0</t>
+  </si>
+  <si>
+    <t>10180002,0_1|10180003,1_1|10180004_1|10180005,3_1</t>
+  </si>
+  <si>
+    <t>10180006,0_2|10180007,1_2|10180008,2_2|10180009,3_2</t>
+  </si>
+  <si>
+    <t>10180010,0_3</t>
+  </si>
+  <si>
+    <t>10180011,0_4|10180011,1_4</t>
+  </si>
+  <si>
     <t>杰克船长</t>
   </si>
   <si>
-    <t>0_3|1_3|2_3</t>
-  </si>
-  <si>
-    <t>0_4</t>
+    <t>10210001,0_0</t>
+  </si>
+  <si>
+    <t>10210002,0_1|10210003,1_1|10210004,2_1|10210005,3_1</t>
+  </si>
+  <si>
+    <t>10210006,0_2|10210007,1_2|10210008,2_2|10210009,3_2</t>
+  </si>
+  <si>
+    <t>10210010,0_3|10210011,1_3|10210012,2_3</t>
+  </si>
+  <si>
+    <t>10210013,0_4</t>
+  </si>
+  <si>
+    <t>10210011,0_5|10210011,1_5</t>
   </si>
 </sst>
 </file>
@@ -746,16 +809,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -765,8 +825,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1082,575 +1142,595 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="10.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.375" style="2" customWidth="1"/>
-    <col min="4" max="5" width="17.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.375" style="3" customWidth="1"/>
-    <col min="8" max="10" width="9" style="3"/>
-    <col min="11" max="11" width="25.75" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="3"/>
+    <col min="2" max="2" width="10.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.375" style="2" customWidth="1"/>
+    <col min="7" max="9" width="9" style="2"/>
+    <col min="10" max="10" width="25.75" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>6</v>
+      <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:5">
+      <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="F4" s="6"/>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
         <v>1001</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>100300</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>1002</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>100300</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="D6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1">
         <v>1003</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>100300</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="2">
-        <v>3</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="D7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1">
         <v>1004</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>1</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>100300</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="2">
-        <v>4</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="D8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1">
         <v>1005</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C9" s="2">
-        <v>103400</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="C9" s="1">
+        <v>100300</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1">
         <v>1006</v>
       </c>
-      <c r="B10" s="2">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2">
+      <c r="B10" s="1">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1">
         <v>103400</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="2">
-        <v>2</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:5">
       <c r="A11" s="1">
         <v>1007</v>
       </c>
-      <c r="B11" s="2">
-        <v>1</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+      <c r="C11" s="1">
         <v>103400</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="2">
-        <v>3</v>
-      </c>
-      <c r="F11" s="7" t="s">
+      <c r="E11" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:5">
       <c r="A12" s="1">
         <v>1008</v>
       </c>
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2">
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
         <v>103400</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="2">
-        <v>4</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="E12" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1">
         <v>1009</v>
       </c>
-      <c r="B13" s="2">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2">
-        <v>103500</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="B13" s="1">
+        <v>2</v>
+      </c>
+      <c r="C13" s="1">
+        <v>103400</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="1">
         <v>1010</v>
       </c>
-      <c r="B14" s="2">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2">
-        <v>103500</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="2">
+      <c r="B14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="C14" s="1">
+        <v>103400</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="1">
         <v>1011</v>
       </c>
-      <c r="B15" s="2">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1">
         <v>103500</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="2">
-        <v>3</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="D15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="1">
         <v>1012</v>
       </c>
-      <c r="B16" s="2">
-        <v>1</v>
-      </c>
-      <c r="C16" s="2">
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1">
         <v>103500</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="2">
-        <v>4</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="D16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1">
         <v>1013</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>2</v>
       </c>
-      <c r="C17" s="2">
-        <v>101700</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="C17" s="1">
+        <v>103500</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1">
         <v>1014</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <v>2</v>
       </c>
-      <c r="C18" s="2">
-        <v>101701</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="2">
-        <v>2</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="C18" s="1">
+        <v>103500</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1">
         <v>1015</v>
       </c>
-      <c r="B19" s="2">
-        <v>2</v>
-      </c>
-      <c r="C19" s="2">
-        <v>101702</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="2">
-        <v>3</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1">
+        <v>103500</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1">
         <v>1016</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="1">
         <v>2</v>
       </c>
-      <c r="C20" s="2">
-        <v>101703</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="2">
-        <v>4</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="C20" s="1">
+        <v>101700</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="1">
         <v>1017</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <v>2</v>
       </c>
-      <c r="C21" s="2">
-        <v>101800</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="2">
-        <v>1</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="C21" s="1">
+        <v>101700</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="1">
         <v>1018</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="1">
         <v>2</v>
       </c>
-      <c r="C22" s="2">
-        <v>101800</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="2">
-        <v>2</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="C22" s="1">
+        <v>101700</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="1">
         <v>1019</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="1">
         <v>2</v>
       </c>
-      <c r="C23" s="2">
-        <v>101800</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="2">
-        <v>3</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="C23" s="1">
+        <v>101700</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="1">
         <v>1020</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="1">
         <v>2</v>
       </c>
-      <c r="C24" s="2">
-        <v>101800</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="2">
-        <v>4</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="C24" s="1">
+        <v>101700</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="1">
         <v>1021</v>
       </c>
-      <c r="B25" s="2">
-        <v>2</v>
-      </c>
-      <c r="C25" s="2">
-        <v>102100</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="2">
-        <v>1</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="B25" s="1">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1">
+        <v>101800</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="1">
         <v>1022</v>
       </c>
-      <c r="B26" s="2">
-        <v>2</v>
-      </c>
-      <c r="C26" s="2">
-        <v>102100</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="2">
-        <v>2</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="B26" s="1">
+        <v>3</v>
+      </c>
+      <c r="C26" s="1">
+        <v>101800</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="1">
         <v>1023</v>
       </c>
-      <c r="B27" s="2">
-        <v>2</v>
-      </c>
-      <c r="C27" s="2">
-        <v>102100</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="2">
+      <c r="B27" s="1">
         <v>3</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="C27" s="1">
+        <v>101800</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="1">
         <v>1024</v>
       </c>
-      <c r="B28" s="2">
-        <v>2</v>
-      </c>
-      <c r="C28" s="2">
-        <v>102100</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="2">
-        <v>4</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="B28" s="1">
+        <v>3</v>
+      </c>
+      <c r="C28" s="1">
+        <v>101800</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="1">
         <v>1025</v>
       </c>
-      <c r="B29" s="2">
-        <v>2</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="1">
+        <v>3</v>
+      </c>
+      <c r="C29" s="1">
+        <v>101800</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1">
+        <v>1026</v>
+      </c>
+      <c r="B30" s="1">
+        <v>4</v>
+      </c>
+      <c r="C30" s="1">
         <v>102100</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="2">
-        <v>5</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>26</v>
+      <c r="D30" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1">
+        <v>1027</v>
+      </c>
+      <c r="B31" s="1">
+        <v>4</v>
+      </c>
+      <c r="C31" s="1">
+        <v>102100</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1">
+        <v>1028</v>
+      </c>
+      <c r="B32" s="1">
+        <v>4</v>
+      </c>
+      <c r="C32" s="1">
+        <v>102100</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1">
+        <v>1029</v>
+      </c>
+      <c r="B33" s="1">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1">
+        <v>102100</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1">
+        <v>1030</v>
+      </c>
+      <c r="B34" s="1">
+        <v>4</v>
+      </c>
+      <c r="C34" s="1">
+        <v>102100</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1">
+        <v>1031</v>
+      </c>
+      <c r="B35" s="1">
+        <v>4</v>
+      </c>
+      <c r="C35" s="1">
+        <v>102100</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/ResearchInstitute.xlsx
+++ b/hall/resources/sample/ResearchInstitute.xlsx
@@ -29,11 +29,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="50">
   <si>
     <t>id</t>
   </si>
   <si>
+    <t>场景id</t>
+  </si>
+  <si>
     <t>研究院等级</t>
   </si>
   <si>
@@ -50,6 +53,9 @@
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>RegionID</t>
   </si>
   <si>
     <t>level</t>
@@ -1142,21 +1148,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="10.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.375" style="2" customWidth="1"/>
-    <col min="7" max="9" width="9" style="2"/>
-    <col min="10" max="10" width="25.75" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="2" max="3" width="10.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.375" style="2" customWidth="1"/>
+    <col min="8" max="10" width="9" style="2"/>
+    <col min="11" max="11" width="25.75" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1169,44 +1175,53 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="E4" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>1001</v>
       </c>
@@ -1214,16 +1229,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
         <v>100300</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>1002</v>
       </c>
@@ -1231,16 +1249,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
         <v>100300</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>1003</v>
       </c>
@@ -1248,16 +1269,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
         <v>100300</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>1004</v>
       </c>
@@ -1265,16 +1289,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
         <v>100300</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="E8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>1005</v>
       </c>
@@ -1282,169 +1309,199 @@
         <v>1</v>
       </c>
       <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
         <v>100300</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="E9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>1006</v>
       </c>
       <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
         <v>2</v>
       </c>
-      <c r="C10" s="1">
+      <c r="D10" s="1">
         <v>103400</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="E10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>1007</v>
       </c>
       <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
         <v>2</v>
       </c>
-      <c r="C11" s="1">
+      <c r="D11" s="1">
         <v>103400</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>1008</v>
       </c>
       <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
         <v>2</v>
       </c>
-      <c r="C12" s="1">
+      <c r="D12" s="1">
         <v>103400</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="E12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>1009</v>
       </c>
       <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
         <v>2</v>
       </c>
-      <c r="C13" s="1">
+      <c r="D13" s="1">
         <v>103400</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="E13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="1">
         <v>1010</v>
       </c>
       <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
         <v>2</v>
       </c>
-      <c r="C14" s="1">
+      <c r="D14" s="1">
         <v>103400</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="E14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="1">
         <v>1011</v>
       </c>
       <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1">
         <v>2</v>
       </c>
-      <c r="C15" s="1">
+      <c r="D15" s="1">
         <v>103500</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="E15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="1">
         <v>1012</v>
       </c>
       <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1">
         <v>2</v>
       </c>
-      <c r="C16" s="1">
+      <c r="D16" s="1">
         <v>103500</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1">
         <v>1013</v>
       </c>
       <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1">
         <v>2</v>
       </c>
-      <c r="C17" s="1">
+      <c r="D17" s="1">
         <v>103500</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="E17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1">
         <v>1014</v>
       </c>
       <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1">
         <v>2</v>
       </c>
-      <c r="C18" s="1">
+      <c r="D18" s="1">
         <v>103500</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="E18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1">
         <v>1015</v>
       </c>
@@ -1452,285 +1509,336 @@
         <v>1</v>
       </c>
       <c r="C19" s="1">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1">
         <v>103500</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="E19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1">
         <v>1016</v>
       </c>
       <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1">
         <v>2</v>
       </c>
-      <c r="C20" s="1">
+      <c r="D20" s="1">
         <v>101700</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="E20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1">
         <v>1017</v>
       </c>
       <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1">
         <v>2</v>
       </c>
-      <c r="C21" s="1">
+      <c r="D21" s="1">
         <v>101700</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="1">
         <v>1018</v>
       </c>
       <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1">
         <v>2</v>
       </c>
-      <c r="C22" s="1">
+      <c r="D22" s="1">
         <v>101700</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="E22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="1">
         <v>1019</v>
       </c>
       <c r="B23" s="1">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1">
         <v>2</v>
       </c>
-      <c r="C23" s="1">
+      <c r="D23" s="1">
         <v>101700</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="E23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="1">
         <v>1020</v>
       </c>
       <c r="B24" s="1">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1">
         <v>2</v>
       </c>
-      <c r="C24" s="1">
+      <c r="D24" s="1">
         <v>101700</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="E24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="1">
         <v>1021</v>
       </c>
       <c r="B25" s="1">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1">
         <v>3</v>
       </c>
-      <c r="C25" s="1">
+      <c r="D25" s="1">
         <v>101800</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="E25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="1">
         <v>1022</v>
       </c>
       <c r="B26" s="1">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1">
         <v>3</v>
       </c>
-      <c r="C26" s="1">
+      <c r="D26" s="1">
         <v>101800</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="1">
         <v>1023</v>
       </c>
       <c r="B27" s="1">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1">
         <v>3</v>
       </c>
-      <c r="C27" s="1">
+      <c r="D27" s="1">
         <v>101800</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="E27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="1">
         <v>1024</v>
       </c>
       <c r="B28" s="1">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1">
         <v>3</v>
       </c>
-      <c r="C28" s="1">
+      <c r="D28" s="1">
         <v>101800</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="E28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="1">
         <v>1025</v>
       </c>
       <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1">
         <v>3</v>
       </c>
-      <c r="C29" s="1">
+      <c r="D29" s="1">
         <v>101800</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="E29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="1">
         <v>1026</v>
       </c>
       <c r="B30" s="1">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1">
         <v>4</v>
       </c>
-      <c r="C30" s="1">
+      <c r="D30" s="1">
         <v>102100</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="E30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="1">
         <v>1027</v>
       </c>
       <c r="B31" s="1">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1">
         <v>4</v>
       </c>
-      <c r="C31" s="1">
+      <c r="D31" s="1">
         <v>102100</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="1">
         <v>1028</v>
       </c>
       <c r="B32" s="1">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1">
         <v>4</v>
       </c>
-      <c r="C32" s="1">
+      <c r="D32" s="1">
         <v>102100</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="E32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="1">
         <v>1029</v>
       </c>
       <c r="B33" s="1">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1">
         <v>4</v>
       </c>
-      <c r="C33" s="1">
+      <c r="D33" s="1">
         <v>102100</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="E33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="1">
         <v>1030</v>
       </c>
       <c r="B34" s="1">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1">
         <v>4</v>
       </c>
-      <c r="C34" s="1">
+      <c r="D34" s="1">
         <v>102100</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="E34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="1">
         <v>1031</v>
       </c>
       <c r="B35" s="1">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1">
         <v>4</v>
       </c>
-      <c r="C35" s="1">
+      <c r="D35" s="1">
         <v>102100</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>47</v>
+      <c r="E35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/ResearchInstitute.xlsx
+++ b/hall/resources/sample/ResearchInstitute.xlsx
@@ -85,7 +85,7 @@
     <t>10030006,0_3</t>
   </si>
   <si>
-    <t>10030007,0_3|10030008,1_3</t>
+    <t>10030007,0_4|10030008,1_4</t>
   </si>
   <si>
     <t>神马飞扬</t>

--- a/hall/resources/sample/ResearchInstitute.xlsx
+++ b/hall/resources/sample/ResearchInstitute.xlsx
@@ -1429,7 +1429,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="1">
         <v>103500</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="1">
         <v>103500</v>
@@ -1469,7 +1469,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="1">
         <v>103500</v>
@@ -1489,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="1">
         <v>103500</v>
@@ -1509,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="1">
         <v>103500</v>
@@ -1529,7 +1529,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="1">
         <v>101700</v>
@@ -1549,7 +1549,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" s="1">
         <v>101700</v>
@@ -1569,7 +1569,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" s="1">
         <v>101700</v>
@@ -1589,7 +1589,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="1">
         <v>101700</v>
@@ -1609,7 +1609,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24" s="1">
         <v>101700</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D25" s="1">
         <v>101800</v>
@@ -1649,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D26" s="1">
         <v>101800</v>
@@ -1669,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D27" s="1">
         <v>101800</v>
@@ -1689,7 +1689,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D28" s="1">
         <v>101800</v>
@@ -1709,7 +1709,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" s="1">
         <v>101800</v>
@@ -1729,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D30" s="1">
         <v>102100</v>
@@ -1749,7 +1749,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D31" s="1">
         <v>102100</v>
@@ -1769,7 +1769,7 @@
         <v>1</v>
       </c>
       <c r="C32" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D32" s="1">
         <v>102100</v>
@@ -1789,7 +1789,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D33" s="1">
         <v>102100</v>
@@ -1809,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D34" s="1">
         <v>102100</v>
@@ -1829,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="C35" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D35" s="1">
         <v>102100</v>

--- a/hall/resources/sample/ResearchInstitute.xlsx
+++ b/hall/resources/sample/ResearchInstitute.xlsx
@@ -85,7 +85,7 @@
     <t>10030006,0_3</t>
   </si>
   <si>
-    <t>10030007,0_4|10030008,1_4</t>
+    <t>10030008,0_4|10030007,1_4</t>
   </si>
   <si>
     <t>神马飞扬</t>

--- a/hall/resources/sample/ResearchInstitute.xlsx
+++ b/hall/resources/sample/ResearchInstitute.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="54">
   <si>
     <t>id</t>
   </si>
@@ -106,6 +106,24 @@
     <t>10340010,0_4|10340011,1_4</t>
   </si>
   <si>
+    <t>虎虎生财</t>
+  </si>
+  <si>
+    <t>10340101,0_0</t>
+  </si>
+  <si>
+    <t>10340102,0_1|10340103,1_1|10340104,2_1|10340105,3_1</t>
+  </si>
+  <si>
+    <t>10340106,0_2|10340107,1_2|10340108,2_2</t>
+  </si>
+  <si>
+    <t>10340109,0_3</t>
+  </si>
+  <si>
+    <t>10340110,0_4|10340111,1_4</t>
+  </si>
+  <si>
     <t>金蛇招财</t>
   </si>
   <si>
@@ -124,61 +142,55 @@
     <t>10350010,0_4|10350011,1_4</t>
   </si>
   <si>
-    <t>圣诞狂欢夜</t>
-  </si>
-  <si>
-    <t>10170001,0_0</t>
-  </si>
-  <si>
-    <t>10170002,0_1|10170003,1_1|10170004,2_1|10170005,3_1</t>
-  </si>
-  <si>
-    <t>10170006,0_2|1017007,1_2|10170008,2_2|10170009,3_2</t>
-  </si>
-  <si>
-    <t>10170010,0_3</t>
-  </si>
-  <si>
-    <t>10170011,0_4|10170011,1_4</t>
-  </si>
-  <si>
-    <t>篮球巨星</t>
-  </si>
-  <si>
-    <t>10180001,0_0</t>
-  </si>
-  <si>
-    <t>10180002,0_1|10180003,1_1|10180004_1|10180005,3_1</t>
-  </si>
-  <si>
-    <t>10180006,0_2|10180007,1_2|10180008,2_2|10180009,3_2</t>
-  </si>
-  <si>
-    <t>10180010,0_3</t>
-  </si>
-  <si>
-    <t>10180011,0_4|10180011,1_4</t>
-  </si>
-  <si>
-    <t>杰克船长</t>
-  </si>
-  <si>
-    <t>10210001,0_0</t>
-  </si>
-  <si>
-    <t>10210002,0_1|10210003,1_1|10210004,2_1|10210005,3_1</t>
-  </si>
-  <si>
-    <t>10210006,0_2|10210007,1_2|10210008,2_2|10210009,3_2</t>
-  </si>
-  <si>
-    <t>10210010,0_3|10210011,1_3|10210012,2_3</t>
-  </si>
-  <si>
-    <t>10210013,0_4</t>
-  </si>
-  <si>
-    <t>10210011,0_5|10210011,1_5</t>
+    <t>金钱兔</t>
+  </si>
+  <si>
+    <t>10350101,0_0</t>
+  </si>
+  <si>
+    <t>10350102,0_1|10350103,1_1|10350104,2_1|10350105,3_1</t>
+  </si>
+  <si>
+    <t>10350106,0_2|10350107,1_2|10350108,2_2</t>
+  </si>
+  <si>
+    <t>10350109,0_3</t>
+  </si>
+  <si>
+    <t>10350110,0_4|10350111,1_4</t>
+  </si>
+  <si>
+    <t>埃及艳后</t>
+  </si>
+  <si>
+    <t>10140001,0_0</t>
+  </si>
+  <si>
+    <t>10140002,0_1|10140003,1_1|10140004,2_1|10140005,3_1</t>
+  </si>
+  <si>
+    <t>10140006,0_2</t>
+  </si>
+  <si>
+    <t>10350007,0_3|10350008,1_3</t>
+  </si>
+  <si>
+    <t>10倍金牛</t>
+  </si>
+  <si>
+    <t>10370001,0_0</t>
+  </si>
+  <si>
+    <t>10370002,0_1|10370003,1_1|10370004,2_1|10370005,3_1</t>
+  </si>
+  <si>
+    <t>10370006,0_2|10370007,1_2|10370008,2_2</t>
+  </si>
+  <si>
+    <t>10370009,0_3</t>
+  </si>
+  <si>
+    <t>10370010,0_4|10370011,1_4</t>
   </si>
 </sst>
 </file>
@@ -1148,7 +1160,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1432,7 +1444,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="1">
-        <v>103500</v>
+        <v>103401</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>25</v>
@@ -1452,7 +1464,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="1">
-        <v>103500</v>
+        <v>103401</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>25</v>
@@ -1472,7 +1484,7 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>103500</v>
+        <v>103401</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>25</v>
@@ -1492,7 +1504,7 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>103500</v>
+        <v>103401</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>25</v>
@@ -1512,7 +1524,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>103500</v>
+        <v>103401</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>25</v>
@@ -1532,7 +1544,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>31</v>
@@ -1552,7 +1564,7 @@
         <v>4</v>
       </c>
       <c r="D21" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>31</v>
@@ -1572,7 +1584,7 @@
         <v>4</v>
       </c>
       <c r="D22" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>31</v>
@@ -1592,7 +1604,7 @@
         <v>4</v>
       </c>
       <c r="D23" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>31</v>
@@ -1612,7 +1624,7 @@
         <v>4</v>
       </c>
       <c r="D24" s="1">
-        <v>101700</v>
+        <v>103500</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>31</v>
@@ -1632,7 +1644,7 @@
         <v>5</v>
       </c>
       <c r="D25" s="1">
-        <v>101800</v>
+        <v>103501</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>37</v>
@@ -1652,7 +1664,7 @@
         <v>5</v>
       </c>
       <c r="D26" s="1">
-        <v>101800</v>
+        <v>103501</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>37</v>
@@ -1672,7 +1684,7 @@
         <v>5</v>
       </c>
       <c r="D27" s="1">
-        <v>101800</v>
+        <v>103501</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>37</v>
@@ -1692,7 +1704,7 @@
         <v>5</v>
       </c>
       <c r="D28" s="1">
-        <v>101800</v>
+        <v>103501</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>37</v>
@@ -1712,7 +1724,7 @@
         <v>5</v>
       </c>
       <c r="D29" s="1">
-        <v>101800</v>
+        <v>103501</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>37</v>
@@ -1732,7 +1744,7 @@
         <v>6</v>
       </c>
       <c r="D30" s="1">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>43</v>
@@ -1752,7 +1764,7 @@
         <v>6</v>
       </c>
       <c r="D31" s="1">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>43</v>
@@ -1772,12 +1784,12 @@
         <v>6</v>
       </c>
       <c r="D32" s="1">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="3" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1792,7 +1804,7 @@
         <v>6</v>
       </c>
       <c r="D33" s="1">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>43</v>
@@ -1809,16 +1821,16 @@
         <v>1</v>
       </c>
       <c r="C34" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" s="1">
-        <v>102100</v>
+        <v>103700</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1829,17 +1841,95 @@
         <v>1</v>
       </c>
       <c r="C35" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D35" s="1">
-        <v>102100</v>
+        <v>103700</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>49</v>
-      </c>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="1">
+        <v>1032</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1">
+        <v>7</v>
+      </c>
+      <c r="D36" s="1">
+        <v>103700</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="1">
+        <v>1033</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1">
+        <v>7</v>
+      </c>
+      <c r="D37" s="1">
+        <v>103700</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="1">
+        <v>1034</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1">
+        <v>7</v>
+      </c>
+      <c r="D38" s="1">
+        <v>103700</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="F39" s="3"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="F40" s="3"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="F42" s="3"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="F43" s="3"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="F44" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/ResearchInstitute.xlsx
+++ b/hall/resources/sample/ResearchInstitute.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
   <si>
     <t>id</t>
   </si>
@@ -124,6 +124,21 @@
     <t>10340110,0_4|10340111,1_4</t>
   </si>
   <si>
+    <t>埃及艳后</t>
+  </si>
+  <si>
+    <t>10140001,0_0</t>
+  </si>
+  <si>
+    <t>10140002,0_1|10140003,1_1|10140004,2_1|10140005,3_1</t>
+  </si>
+  <si>
+    <t>10140006,0_2</t>
+  </si>
+  <si>
+    <t>10350007,0_3|10350008,1_3</t>
+  </si>
+  <si>
     <t>金蛇招财</t>
   </si>
   <si>
@@ -160,19 +175,19 @@
     <t>10350110,0_4|10350111,1_4</t>
   </si>
   <si>
-    <t>埃及艳后</t>
-  </si>
-  <si>
-    <t>10140001,0_0</t>
-  </si>
-  <si>
-    <t>10140002,0_1|10140003,1_1|10140004,2_1|10140005,3_1</t>
-  </si>
-  <si>
-    <t>10140006,0_2</t>
-  </si>
-  <si>
-    <t>10350007,0_3|10350008,1_3</t>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>10070001,0_0</t>
+  </si>
+  <si>
+    <t>10070002,0_1|10070003,1_1|10070004,2_1|10070005,3_1|10070006,4_1</t>
+  </si>
+  <si>
+    <t>10070007,0_2|10070008,1_2|10070009,2_2</t>
+  </si>
+  <si>
+    <t>10070010,0_3|10070011,1_3</t>
   </si>
   <si>
     <t>10倍金牛</t>
@@ -191,6 +206,42 @@
   </si>
   <si>
     <t>10370010,0_4|10370011,1_4</t>
+  </si>
+  <si>
+    <t>鼠鼠福福</t>
+  </si>
+  <si>
+    <t>10360001,0_0</t>
+  </si>
+  <si>
+    <t>10360002,0_1|10360003,1_1|10360004,2_1|10360005,3_1</t>
+  </si>
+  <si>
+    <t>10360006,0_2|10360007,1_2|10360008,2_2</t>
+  </si>
+  <si>
+    <t>10360009,0_3</t>
+  </si>
+  <si>
+    <t>10360010,0_4|10360011,1_4</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜</t>
+  </si>
+  <si>
+    <t>10170001,0_0</t>
+  </si>
+  <si>
+    <t>10170002,0_1|10170003,1_1|10170004,2_1|10170005,3_1|10170006,4_1</t>
+  </si>
+  <si>
+    <t>10170007,0_2|10170008,1_2|10170009,2_2</t>
+  </si>
+  <si>
+    <t>10170010,0_3</t>
+  </si>
+  <si>
+    <t>10170011,0_4|10170012,1_4</t>
   </si>
 </sst>
 </file>
@@ -1160,7 +1211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1544,7 +1595,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>103500</v>
+        <v>101400</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>31</v>
@@ -1564,7 +1615,7 @@
         <v>4</v>
       </c>
       <c r="D21" s="1">
-        <v>103500</v>
+        <v>101400</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>31</v>
@@ -1584,12 +1635,12 @@
         <v>4</v>
       </c>
       <c r="D22" s="1">
-        <v>103500</v>
+        <v>101400</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="3" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1604,7 +1655,7 @@
         <v>4</v>
       </c>
       <c r="D23" s="1">
-        <v>103500</v>
+        <v>101400</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>31</v>
@@ -1621,16 +1672,16 @@
         <v>1</v>
       </c>
       <c r="C24" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" s="1">
         <v>103500</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1644,10 +1695,10 @@
         <v>5</v>
       </c>
       <c r="D25" s="1">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>38</v>
@@ -1664,12 +1715,12 @@
         <v>5</v>
       </c>
       <c r="D26" s="1">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1684,12 +1735,12 @@
         <v>5</v>
       </c>
       <c r="D27" s="1">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F27" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1704,10 +1755,10 @@
         <v>5</v>
       </c>
       <c r="D28" s="1">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>41</v>
@@ -1721,16 +1772,16 @@
         <v>1</v>
       </c>
       <c r="C29" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" s="1">
         <v>103501</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1744,10 +1795,10 @@
         <v>6</v>
       </c>
       <c r="D30" s="1">
-        <v>101400</v>
+        <v>103501</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>44</v>
@@ -1764,12 +1815,12 @@
         <v>6</v>
       </c>
       <c r="D31" s="1">
-        <v>101400</v>
+        <v>103501</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="6" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1784,10 +1835,10 @@
         <v>6</v>
       </c>
       <c r="D32" s="1">
-        <v>101400</v>
+        <v>103501</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>46</v>
@@ -1804,10 +1855,10 @@
         <v>6</v>
       </c>
       <c r="D33" s="1">
-        <v>101400</v>
+        <v>103501</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>47</v>
@@ -1824,7 +1875,7 @@
         <v>7</v>
       </c>
       <c r="D34" s="1">
-        <v>103700</v>
+        <v>100700</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>48</v>
@@ -1844,7 +1895,7 @@
         <v>7</v>
       </c>
       <c r="D35" s="1">
-        <v>103700</v>
+        <v>100700</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>48</v>
@@ -1864,7 +1915,7 @@
         <v>7</v>
       </c>
       <c r="D36" s="1">
-        <v>103700</v>
+        <v>100700</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>48</v>
@@ -1884,7 +1935,7 @@
         <v>7</v>
       </c>
       <c r="D37" s="1">
-        <v>103700</v>
+        <v>100700</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>48</v>
@@ -1901,35 +1952,297 @@
         <v>1</v>
       </c>
       <c r="C38" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D38" s="1">
         <v>103700</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F38" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="1">
+        <v>1035</v>
+      </c>
+      <c r="B39" s="1">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1">
+        <v>8</v>
+      </c>
+      <c r="D39" s="1">
+        <v>103700</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="F39" s="3"/>
+      <c r="F39" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="F40" s="3"/>
+      <c r="A40" s="1">
+        <v>1036</v>
+      </c>
+      <c r="B40" s="1">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1">
+        <v>8</v>
+      </c>
+      <c r="D40" s="1">
+        <v>103700</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="F41" s="6"/>
+      <c r="A41" s="1">
+        <v>1037</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1">
+        <v>8</v>
+      </c>
+      <c r="D41" s="1">
+        <v>103700</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="F42" s="3"/>
+      <c r="A42" s="1">
+        <v>1038</v>
+      </c>
+      <c r="B42" s="1">
+        <v>1</v>
+      </c>
+      <c r="C42" s="1">
+        <v>8</v>
+      </c>
+      <c r="D42" s="1">
+        <v>103700</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="F43" s="3"/>
+      <c r="A43" s="1">
+        <v>1039</v>
+      </c>
+      <c r="B43" s="1">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1">
+        <v>9</v>
+      </c>
+      <c r="D43" s="1">
+        <v>103600</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="F44" s="3"/>
+      <c r="A44" s="1">
+        <v>1040</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1</v>
+      </c>
+      <c r="C44" s="1">
+        <v>9</v>
+      </c>
+      <c r="D44" s="1">
+        <v>103600</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="1">
+        <v>1041</v>
+      </c>
+      <c r="B45" s="1">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1">
+        <v>9</v>
+      </c>
+      <c r="D45" s="1">
+        <v>103600</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="1">
+        <v>1042</v>
+      </c>
+      <c r="B46" s="1">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1">
+        <v>9</v>
+      </c>
+      <c r="D46" s="1">
+        <v>103600</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="1">
+        <v>1043</v>
+      </c>
+      <c r="B47" s="1">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1">
+        <v>9</v>
+      </c>
+      <c r="D47" s="1">
+        <v>103600</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="1">
+        <v>1044</v>
+      </c>
+      <c r="B48" s="1">
+        <v>1</v>
+      </c>
+      <c r="C48" s="1">
+        <v>10</v>
+      </c>
+      <c r="D48" s="1">
+        <v>101700</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="1">
+        <v>1045</v>
+      </c>
+      <c r="B49" s="1">
+        <v>1</v>
+      </c>
+      <c r="C49" s="1">
+        <v>10</v>
+      </c>
+      <c r="D49" s="1">
+        <v>101700</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="1">
+        <v>1046</v>
+      </c>
+      <c r="B50" s="1">
+        <v>1</v>
+      </c>
+      <c r="C50" s="1">
+        <v>10</v>
+      </c>
+      <c r="D50" s="1">
+        <v>101700</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="1">
+        <v>1047</v>
+      </c>
+      <c r="B51" s="1">
+        <v>1</v>
+      </c>
+      <c r="C51" s="1">
+        <v>10</v>
+      </c>
+      <c r="D51" s="1">
+        <v>101700</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="1">
+        <v>1048</v>
+      </c>
+      <c r="B52" s="1">
+        <v>1</v>
+      </c>
+      <c r="C52" s="1">
+        <v>10</v>
+      </c>
+      <c r="D52" s="1">
+        <v>101700</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/ResearchInstitute.xlsx
+++ b/hall/resources/sample/ResearchInstitute.xlsx
@@ -136,7 +136,7 @@
     <t>10140006,0_2</t>
   </si>
   <si>
-    <t>10350007,0_3|10350008,1_3</t>
+    <t>10140007,0_3|10140008,1_3</t>
   </si>
   <si>
     <t>金蛇招财</t>

--- a/hall/resources/sample/ResearchInstitute.xlsx
+++ b/hall/resources/sample/ResearchInstitute.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="77">
   <si>
     <t>id</t>
   </si>
@@ -242,6 +242,24 @@
   </si>
   <si>
     <t>10170011,0_4|10170012,1_4</t>
+  </si>
+  <si>
+    <t>财神到</t>
+  </si>
+  <si>
+    <t>10120001,0_0</t>
+  </si>
+  <si>
+    <t>10120002,0_1|10120003,1_1|10120004,2_1|10120005,3_1</t>
+  </si>
+  <si>
+    <t>10120006,0_2</t>
+  </si>
+  <si>
+    <t>10120007,0_3</t>
+  </si>
+  <si>
+    <t>10120008,0_4|10120009,1_4</t>
   </si>
 </sst>
 </file>
@@ -1211,7 +1229,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1952,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D38" s="1">
         <v>103700</v>
@@ -1972,7 +1990,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D39" s="1">
         <v>103700</v>
@@ -1992,7 +2010,7 @@
         <v>1</v>
       </c>
       <c r="C40" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D40" s="1">
         <v>103700</v>
@@ -2012,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="C41" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D41" s="1">
         <v>103700</v>
@@ -2032,7 +2050,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D42" s="1">
         <v>103700</v>
@@ -2242,6 +2260,106 @@
       </c>
       <c r="F52" s="3" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="1">
+        <v>1049</v>
+      </c>
+      <c r="B53" s="1">
+        <v>1</v>
+      </c>
+      <c r="C53" s="1">
+        <v>8</v>
+      </c>
+      <c r="D53" s="1">
+        <v>101200</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="1">
+        <v>1050</v>
+      </c>
+      <c r="B54" s="1">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1">
+        <v>8</v>
+      </c>
+      <c r="D54" s="1">
+        <v>101200</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="1">
+        <v>1051</v>
+      </c>
+      <c r="B55" s="1">
+        <v>1</v>
+      </c>
+      <c r="C55" s="1">
+        <v>8</v>
+      </c>
+      <c r="D55" s="1">
+        <v>101200</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="1">
+        <v>1052</v>
+      </c>
+      <c r="B56" s="1">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1">
+        <v>8</v>
+      </c>
+      <c r="D56" s="1">
+        <v>101200</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="1">
+        <v>1053</v>
+      </c>
+      <c r="B57" s="1">
+        <v>1</v>
+      </c>
+      <c r="C57" s="1">
+        <v>8</v>
+      </c>
+      <c r="D57" s="1">
+        <v>101200</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/ResearchInstitute.xlsx
+++ b/hall/resources/sample/ResearchInstitute.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
   <si>
     <t>id</t>
   </si>
@@ -188,24 +188,6 @@
   </si>
   <si>
     <t>10070010,0_3|10070011,1_3</t>
-  </si>
-  <si>
-    <t>10倍金牛</t>
-  </si>
-  <si>
-    <t>10370001,0_0</t>
-  </si>
-  <si>
-    <t>10370002,0_1|10370003,1_1|10370004,2_1|10370005,3_1</t>
-  </si>
-  <si>
-    <t>10370006,0_2|10370007,1_2|10370008,2_2</t>
-  </si>
-  <si>
-    <t>10370009,0_3</t>
-  </si>
-  <si>
-    <t>10370010,0_4|10370011,1_4</t>
   </si>
   <si>
     <t>鼠鼠福福</t>
@@ -1229,7 +1211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1964,16 +1946,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="B38" s="1">
         <v>1</v>
       </c>
       <c r="C38" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D38" s="1">
-        <v>103700</v>
+        <v>103600</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>53</v>
@@ -1984,16 +1966,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="1">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="B39" s="1">
         <v>1</v>
       </c>
       <c r="C39" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D39" s="1">
-        <v>103700</v>
+        <v>103600</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>53</v>
@@ -2004,16 +1986,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="1">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="B40" s="1">
         <v>1</v>
       </c>
       <c r="C40" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D40" s="1">
-        <v>103700</v>
+        <v>103600</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>53</v>
@@ -2024,16 +2006,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="B41" s="1">
         <v>1</v>
       </c>
       <c r="C41" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D41" s="1">
-        <v>103700</v>
+        <v>103600</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>53</v>
@@ -2044,16 +2026,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="B42" s="1">
         <v>1</v>
       </c>
       <c r="C42" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D42" s="1">
-        <v>103700</v>
+        <v>103600</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>53</v>
@@ -2064,16 +2046,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="1">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="B43" s="1">
         <v>1</v>
       </c>
       <c r="C43" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D43" s="1">
-        <v>103600</v>
+        <v>101700</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>59</v>
@@ -2084,16 +2066,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="1">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="B44" s="1">
         <v>1</v>
       </c>
       <c r="C44" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D44" s="1">
-        <v>103600</v>
+        <v>101700</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>59</v>
@@ -2104,16 +2086,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="1">
-        <v>1041</v>
+        <v>1046</v>
       </c>
       <c r="B45" s="1">
         <v>1</v>
       </c>
       <c r="C45" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D45" s="1">
-        <v>103600</v>
+        <v>101700</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>59</v>
@@ -2124,16 +2106,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="1">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="B46" s="1">
         <v>1</v>
       </c>
       <c r="C46" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D46" s="1">
-        <v>103600</v>
+        <v>101700</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>59</v>
@@ -2144,16 +2126,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="1">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="B47" s="1">
         <v>1</v>
       </c>
       <c r="C47" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D47" s="1">
-        <v>103600</v>
+        <v>101700</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>59</v>
@@ -2164,16 +2146,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="1">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="B48" s="1">
         <v>1</v>
       </c>
       <c r="C48" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D48" s="1">
-        <v>101700</v>
+        <v>101200</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>65</v>
@@ -2184,16 +2166,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="1">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="B49" s="1">
         <v>1</v>
       </c>
       <c r="C49" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D49" s="1">
-        <v>101700</v>
+        <v>101200</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>65</v>
@@ -2204,16 +2186,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="1">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="B50" s="1">
         <v>1</v>
       </c>
       <c r="C50" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D50" s="1">
-        <v>101700</v>
+        <v>101200</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>65</v>
@@ -2224,16 +2206,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="1">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="B51" s="1">
         <v>1</v>
       </c>
       <c r="C51" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D51" s="1">
-        <v>101700</v>
+        <v>101200</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>65</v>
@@ -2244,122 +2226,22 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="B52" s="1">
         <v>1</v>
       </c>
       <c r="C52" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D52" s="1">
-        <v>101700</v>
+        <v>101200</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="1">
-        <v>1049</v>
-      </c>
-      <c r="B53" s="1">
-        <v>1</v>
-      </c>
-      <c r="C53" s="1">
-        <v>8</v>
-      </c>
-      <c r="D53" s="1">
-        <v>101200</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="1">
-        <v>1050</v>
-      </c>
-      <c r="B54" s="1">
-        <v>1</v>
-      </c>
-      <c r="C54" s="1">
-        <v>8</v>
-      </c>
-      <c r="D54" s="1">
-        <v>101200</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="1">
-        <v>1051</v>
-      </c>
-      <c r="B55" s="1">
-        <v>1</v>
-      </c>
-      <c r="C55" s="1">
-        <v>8</v>
-      </c>
-      <c r="D55" s="1">
-        <v>101200</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="1">
-        <v>1052</v>
-      </c>
-      <c r="B56" s="1">
-        <v>1</v>
-      </c>
-      <c r="C56" s="1">
-        <v>8</v>
-      </c>
-      <c r="D56" s="1">
-        <v>101200</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="1">
-        <v>1053</v>
-      </c>
-      <c r="B57" s="1">
-        <v>1</v>
-      </c>
-      <c r="C57" s="1">
-        <v>8</v>
-      </c>
-      <c r="D57" s="1">
-        <v>101200</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/ResearchInstitute.xlsx
+++ b/hall/resources/sample/ResearchInstitute.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="74">
   <si>
     <t>id</t>
   </si>
@@ -88,93 +88,6 @@
     <t>10030008,0_4|10030007,1_4</t>
   </si>
   <si>
-    <t>神马飞扬</t>
-  </si>
-  <si>
-    <t>10340001,0_0</t>
-  </si>
-  <si>
-    <t>10340002,0_1|10340003,1_1|10340004,2_1|10340005,3_1</t>
-  </si>
-  <si>
-    <t>10340006,0_2|10340007,1_2|10340008,2_2</t>
-  </si>
-  <si>
-    <t>10340009,0_3</t>
-  </si>
-  <si>
-    <t>10340010,0_4|10340011,1_4</t>
-  </si>
-  <si>
-    <t>虎虎生财</t>
-  </si>
-  <si>
-    <t>10340101,0_0</t>
-  </si>
-  <si>
-    <t>10340102,0_1|10340103,1_1|10340104,2_1|10340105,3_1</t>
-  </si>
-  <si>
-    <t>10340106,0_2|10340107,1_2|10340108,2_2</t>
-  </si>
-  <si>
-    <t>10340109,0_3</t>
-  </si>
-  <si>
-    <t>10340110,0_4|10340111,1_4</t>
-  </si>
-  <si>
-    <t>埃及艳后</t>
-  </si>
-  <si>
-    <t>10140001,0_0</t>
-  </si>
-  <si>
-    <t>10140002,0_1|10140003,1_1|10140004,2_1|10140005,3_1</t>
-  </si>
-  <si>
-    <t>10140006,0_2</t>
-  </si>
-  <si>
-    <t>10140007,0_3|10140008,1_3</t>
-  </si>
-  <si>
-    <t>金蛇招财</t>
-  </si>
-  <si>
-    <t>10350001,0_0</t>
-  </si>
-  <si>
-    <t>10350002,0_1|10350003,1_1|10350004,2_1|10350005,3_1</t>
-  </si>
-  <si>
-    <t>10350006,0_2|10350007,1_2|10350008,2_2</t>
-  </si>
-  <si>
-    <t>10350009,0_3</t>
-  </si>
-  <si>
-    <t>10350010,0_4|10350011,1_4</t>
-  </si>
-  <si>
-    <t>金钱兔</t>
-  </si>
-  <si>
-    <t>10350101,0_0</t>
-  </si>
-  <si>
-    <t>10350102,0_1|10350103,1_1|10350104,2_1|10350105,3_1</t>
-  </si>
-  <si>
-    <t>10350106,0_2|10350107,1_2|10350108,2_2</t>
-  </si>
-  <si>
-    <t>10350109,0_3</t>
-  </si>
-  <si>
-    <t>10350110,0_4|10350111,1_4</t>
-  </si>
-  <si>
     <t>麻将胡了</t>
   </si>
   <si>
@@ -190,42 +103,6 @@
     <t>10070010,0_3|10070011,1_3</t>
   </si>
   <si>
-    <t>鼠鼠福福</t>
-  </si>
-  <si>
-    <t>10360001,0_0</t>
-  </si>
-  <si>
-    <t>10360002,0_1|10360003,1_1|10360004,2_1|10360005,3_1</t>
-  </si>
-  <si>
-    <t>10360006,0_2|10360007,1_2|10360008,2_2</t>
-  </si>
-  <si>
-    <t>10360009,0_3</t>
-  </si>
-  <si>
-    <t>10360010,0_4|10360011,1_4</t>
-  </si>
-  <si>
-    <t>圣诞狂欢夜</t>
-  </si>
-  <si>
-    <t>10170001,0_0</t>
-  </si>
-  <si>
-    <t>10170002,0_1|10170003,1_1|10170004,2_1|10170005,3_1|10170006,4_1</t>
-  </si>
-  <si>
-    <t>10170007,0_2|10170008,1_2|10170009,2_2</t>
-  </si>
-  <si>
-    <t>10170010,0_3</t>
-  </si>
-  <si>
-    <t>10170011,0_4|10170012,1_4</t>
-  </si>
-  <si>
     <t>财神到</t>
   </si>
   <si>
@@ -242,6 +119,138 @@
   </si>
   <si>
     <t>10120008,0_4|10120009,1_4</t>
+  </si>
+  <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>10180001,0_0</t>
+  </si>
+  <si>
+    <t>10180002,0_1|10180003,1_1|10180004,2_1|10180005,3_1|10180006,4_1</t>
+  </si>
+  <si>
+    <t>10180007,0_2|10180008,1_2|10180009,2_2</t>
+  </si>
+  <si>
+    <t>10180010,0_3</t>
+  </si>
+  <si>
+    <t>10180011,0_4|10180012,1_4</t>
+  </si>
+  <si>
+    <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>10250001,0_0</t>
+  </si>
+  <si>
+    <t>10250002,0_1|10250003,1_1|10250004,2_1|10250005,3_1|10250006,4_1</t>
+  </si>
+  <si>
+    <t>10250007,0_2|10250008,1_2|10250009,2_2</t>
+  </si>
+  <si>
+    <t>10250010,0_3</t>
+  </si>
+  <si>
+    <t>10250011,0_4|10250012,1_4</t>
+  </si>
+  <si>
+    <t>绿巨人</t>
+  </si>
+  <si>
+    <t>10310001,0_0</t>
+  </si>
+  <si>
+    <t>10310002,0_1|10310003,1_1|10310004,2_1|10310005,3_1</t>
+  </si>
+  <si>
+    <t>10310006,0_2|10310007,1_2|10310008,2_2</t>
+  </si>
+  <si>
+    <t>10310009,0_3|10310010,1_3|10310011,2_3</t>
+  </si>
+  <si>
+    <t>10310012,0_4</t>
+  </si>
+  <si>
+    <t>10310013,0_5|10310014,1_5</t>
+  </si>
+  <si>
+    <t>雷神</t>
+  </si>
+  <si>
+    <t>10220001,0_0</t>
+  </si>
+  <si>
+    <t>10220002,0_1|10220003,1_1|10220004,2_1|10220005,3_1</t>
+  </si>
+  <si>
+    <t>10220006,0_2|10220007,1_2|10220008,2_2</t>
+  </si>
+  <si>
+    <t>10220009,0_3</t>
+  </si>
+  <si>
+    <t>10220010,0_4|10220011,1_4</t>
+  </si>
+  <si>
+    <t>杰克船长</t>
+  </si>
+  <si>
+    <t>10210001,0_0</t>
+  </si>
+  <si>
+    <t>10210002,0_1|10210003,1_1|10210004,2_1|10210005,3_1|10210006,4_1</t>
+  </si>
+  <si>
+    <t>10210007,0_2|10210008,1_2|10210009,2_2</t>
+  </si>
+  <si>
+    <t>10210010,0_3|10210011,1_3|10210012,2_3</t>
+  </si>
+  <si>
+    <t>10210013,0_4</t>
+  </si>
+  <si>
+    <t>10210014,0_5|10210015,1_5</t>
+  </si>
+  <si>
+    <t>愤怒的小鸟</t>
+  </si>
+  <si>
+    <t>10390001,0_0</t>
+  </si>
+  <si>
+    <t>10390002,0_1|10390003,1_1|10390004,2_1|10390005,3_1|10390006,4_1</t>
+  </si>
+  <si>
+    <t>10390007,0_2|10390008,1_2|10390009,2_2</t>
+  </si>
+  <si>
+    <t>10390010,0_3</t>
+  </si>
+  <si>
+    <t>10390011,0_4|10390012,1_4</t>
+  </si>
+  <si>
+    <t>宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>10200001,0_0</t>
+  </si>
+  <si>
+    <t>10200002,0_1|10200003,1_1|10200004,2_1|10200005,3_1|10200006,4_1</t>
+  </si>
+  <si>
+    <t>10200007,0_2|10200008,1_2|10200009,2_2</t>
+  </si>
+  <si>
+    <t>10200010,0_3</t>
+  </si>
+  <si>
+    <t>10200011,0_4|10200012,1_4</t>
   </si>
 </sst>
 </file>
@@ -1211,7 +1220,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1395,7 +1404,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1">
-        <v>103400</v>
+        <v>100700</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>19</v>
@@ -1415,7 +1424,7 @@
         <v>2</v>
       </c>
       <c r="D11" s="1">
-        <v>103400</v>
+        <v>100700</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>19</v>
@@ -1435,7 +1444,7 @@
         <v>2</v>
       </c>
       <c r="D12" s="1">
-        <v>103400</v>
+        <v>100700</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>19</v>
@@ -1455,7 +1464,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="1">
-        <v>103400</v>
+        <v>100700</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>19</v>
@@ -1472,16 +1481,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="1">
-        <v>103400</v>
+        <v>101200</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1495,10 +1504,10 @@
         <v>3</v>
       </c>
       <c r="D15" s="1">
-        <v>103401</v>
+        <v>101200</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>26</v>
@@ -1515,12 +1524,12 @@
         <v>3</v>
       </c>
       <c r="D16" s="1">
-        <v>103401</v>
+        <v>101200</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1535,12 +1544,12 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>103401</v>
+        <v>101200</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1555,10 +1564,10 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>103401</v>
+        <v>101200</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>29</v>
@@ -1572,16 +1581,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" s="1">
-        <v>103401</v>
+        <v>101800</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1595,10 +1604,10 @@
         <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>101400</v>
+        <v>101800</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>32</v>
@@ -1615,12 +1624,12 @@
         <v>4</v>
       </c>
       <c r="D21" s="1">
-        <v>101400</v>
+        <v>101800</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1635,10 +1644,10 @@
         <v>4</v>
       </c>
       <c r="D22" s="1">
-        <v>101400</v>
+        <v>101800</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>34</v>
@@ -1655,10 +1664,10 @@
         <v>4</v>
       </c>
       <c r="D23" s="1">
-        <v>101400</v>
+        <v>101800</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>35</v>
@@ -1675,7 +1684,7 @@
         <v>5</v>
       </c>
       <c r="D24" s="1">
-        <v>103500</v>
+        <v>102500</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>36</v>
@@ -1695,7 +1704,7 @@
         <v>5</v>
       </c>
       <c r="D25" s="1">
-        <v>103500</v>
+        <v>102500</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>36</v>
@@ -1715,7 +1724,7 @@
         <v>5</v>
       </c>
       <c r="D26" s="1">
-        <v>103500</v>
+        <v>102500</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>36</v>
@@ -1735,7 +1744,7 @@
         <v>5</v>
       </c>
       <c r="D27" s="1">
-        <v>103500</v>
+        <v>102500</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>36</v>
@@ -1755,7 +1764,7 @@
         <v>5</v>
       </c>
       <c r="D28" s="1">
-        <v>103500</v>
+        <v>102500</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>36</v>
@@ -1775,7 +1784,7 @@
         <v>6</v>
       </c>
       <c r="D29" s="1">
-        <v>103501</v>
+        <v>103100</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>42</v>
@@ -1795,7 +1804,7 @@
         <v>6</v>
       </c>
       <c r="D30" s="1">
-        <v>103501</v>
+        <v>103100</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>42</v>
@@ -1815,7 +1824,7 @@
         <v>6</v>
       </c>
       <c r="D31" s="1">
-        <v>103501</v>
+        <v>103100</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>42</v>
@@ -1835,12 +1844,12 @@
         <v>6</v>
       </c>
       <c r="D32" s="1">
-        <v>103501</v>
+        <v>103100</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="6" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1855,7 +1864,7 @@
         <v>6</v>
       </c>
       <c r="D33" s="1">
-        <v>103501</v>
+        <v>103100</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>42</v>
@@ -1872,16 +1881,16 @@
         <v>1</v>
       </c>
       <c r="C34" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D34" s="1">
-        <v>100700</v>
+        <v>103100</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1895,10 +1904,10 @@
         <v>7</v>
       </c>
       <c r="D35" s="1">
-        <v>100700</v>
+        <v>102200</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>50</v>
@@ -1915,12 +1924,12 @@
         <v>7</v>
       </c>
       <c r="D36" s="1">
-        <v>100700</v>
+        <v>102200</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F36" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1935,90 +1944,90 @@
         <v>7</v>
       </c>
       <c r="D37" s="1">
-        <v>100700</v>
+        <v>102200</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F37" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="B38" s="1">
         <v>1</v>
       </c>
       <c r="C38" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D38" s="1">
-        <v>103600</v>
+        <v>102200</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="1">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="B39" s="1">
         <v>1</v>
       </c>
       <c r="C39" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D39" s="1">
-        <v>103600</v>
+        <v>102200</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="1">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="B40" s="1">
         <v>1</v>
       </c>
       <c r="C40" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" s="1">
-        <v>103600</v>
+        <v>102100</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F40" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="B41" s="1">
         <v>1</v>
       </c>
       <c r="C41" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41" s="1">
-        <v>103600</v>
+        <v>102100</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>57</v>
@@ -2026,99 +2035,99 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="B42" s="1">
         <v>1</v>
       </c>
       <c r="C42" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42" s="1">
-        <v>103600</v>
+        <v>102100</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F42" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F42" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="1">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B43" s="1">
         <v>1</v>
       </c>
       <c r="C43" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D43" s="1">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F43" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="1">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="B44" s="1">
         <v>1</v>
       </c>
       <c r="C44" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D44" s="1">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="1">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="B45" s="1">
         <v>1</v>
       </c>
       <c r="C45" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D45" s="1">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>62</v>
+        <v>55</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="1">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="B46" s="1">
         <v>1</v>
       </c>
       <c r="C46" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D46" s="1">
-        <v>101700</v>
+        <v>103900</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>63</v>
@@ -2126,19 +2135,19 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="1">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="B47" s="1">
         <v>1</v>
       </c>
       <c r="C47" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D47" s="1">
-        <v>101700</v>
+        <v>103900</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>64</v>
@@ -2146,79 +2155,79 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="1">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="B48" s="1">
         <v>1</v>
       </c>
       <c r="C48" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D48" s="1">
-        <v>101200</v>
+        <v>103900</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F48" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="1">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="B49" s="1">
         <v>1</v>
       </c>
       <c r="C49" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D49" s="1">
-        <v>101200</v>
+        <v>103900</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="1">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="B50" s="1">
         <v>1</v>
       </c>
       <c r="C50" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D50" s="1">
-        <v>101200</v>
+        <v>103900</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="1">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="B51" s="1">
         <v>1</v>
       </c>
       <c r="C51" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D51" s="1">
-        <v>101200</v>
+        <v>102000</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>69</v>
@@ -2226,22 +2235,82 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="B52" s="1">
         <v>1</v>
       </c>
       <c r="C52" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D52" s="1">
-        <v>101200</v>
+        <v>102000</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="1">
+        <v>1049</v>
+      </c>
+      <c r="B53" s="1">
+        <v>1</v>
+      </c>
+      <c r="C53" s="1">
+        <v>10</v>
+      </c>
+      <c r="D53" s="1">
+        <v>102000</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="1">
+        <v>1050</v>
+      </c>
+      <c r="B54" s="1">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1">
+        <v>10</v>
+      </c>
+      <c r="D54" s="1">
+        <v>102000</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="1">
+        <v>1051</v>
+      </c>
+      <c r="B55" s="1">
+        <v>1</v>
+      </c>
+      <c r="C55" s="1">
+        <v>10</v>
+      </c>
+      <c r="D55" s="1">
+        <v>102000</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/ResearchInstitute.xlsx
+++ b/hall/resources/sample/ResearchInstitute.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
   <si>
     <t>id</t>
   </si>
@@ -70,43 +75,82 @@
     <t>client</t>
   </si>
   <si>
+    <t>愤怒的小鸟</t>
+  </si>
+  <si>
+    <t>10390011,0_0|10390012,1_0|10390001,2_0</t>
+  </si>
+  <si>
+    <t>10390002,0_1|10390003,1_1|10390004,2_1|10390005,3_1|10390006,4_1</t>
+  </si>
+  <si>
+    <t>10390007,0_2|10390008,1_2|10390009,2_2</t>
+  </si>
+  <si>
+    <t>10390010,0_3</t>
+  </si>
+  <si>
+    <t>象财神</t>
+  </si>
+  <si>
+    <t>10270010,0_0|10270011,1_0|10270001,2_0</t>
+  </si>
+  <si>
+    <t>10270002,0_1|10270003,1_1|10270004,2_1|10270005</t>
+  </si>
+  <si>
+    <t>10270006,0_2|10270007,1_2|10270008,2_2</t>
+  </si>
+  <si>
+    <t>10270009,0_3</t>
+  </si>
+  <si>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>10070010,0_0|10070011,1_0|10070001,2_0</t>
+  </si>
+  <si>
+    <t>10070002,0_1|10070003,1_1|10070004,2_1|10070005,3_1|10070006,4_1</t>
+  </si>
+  <si>
+    <t>10070007,0_2|10070008,1_2|10070009,2_2</t>
+  </si>
+  <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>10180011,0_0|10180012,1_0|10180001,2_0</t>
+  </si>
+  <si>
+    <t>10180002,0_1|10180003,1_1|10180004,2_1|10180005,3_1|10180006,4_1</t>
+  </si>
+  <si>
+    <t>10180007,0_2|10180008,1_2|10180009,2_2</t>
+  </si>
+  <si>
+    <t>10180010,0_3</t>
+  </si>
+  <si>
     <t>超级明星</t>
   </si>
   <si>
-    <t>10030001,0_0</t>
-  </si>
-  <si>
-    <t>10030002,0_1|10030003,1_1|10030004,2_1</t>
-  </si>
-  <si>
-    <t>10030005,0_2</t>
-  </si>
-  <si>
-    <t>10030006,0_3</t>
-  </si>
-  <si>
-    <t>10030008,0_4|10030007,1_4</t>
-  </si>
-  <si>
-    <t>麻将胡了</t>
-  </si>
-  <si>
-    <t>10070001,0_0</t>
-  </si>
-  <si>
-    <t>10070002,0_1|10070003,1_1|10070004,2_1|10070005,3_1|10070006,4_1</t>
-  </si>
-  <si>
-    <t>10070007,0_2|10070008,1_2|10070009,2_2</t>
-  </si>
-  <si>
-    <t>10070010,0_3|10070011,1_3</t>
+    <t>10030010,0_0|10030009,1_0|10030001,2_0</t>
+  </si>
+  <si>
+    <t>10030002,0_1|10030003,1_1|10030004,2_1|10030005,3_1|10030006,4_1</t>
+  </si>
+  <si>
+    <t>10030007,0_2</t>
+  </si>
+  <si>
+    <t>10030008,0_3</t>
   </si>
   <si>
     <t>财神到</t>
   </si>
   <si>
-    <t>10120001,0_0</t>
+    <t>10120008,0_0|10120009,1_0|10120001,2_0</t>
   </si>
   <si>
     <t>10120002,0_1|10120003,1_1|10120004,2_1|10120005,3_1</t>
@@ -118,31 +162,10 @@
     <t>10120007,0_3</t>
   </si>
   <si>
-    <t>10120008,0_4|10120009,1_4</t>
-  </si>
-  <si>
-    <t>篮球巨星</t>
-  </si>
-  <si>
-    <t>10180001,0_0</t>
-  </si>
-  <si>
-    <t>10180002,0_1|10180003,1_1|10180004,2_1|10180005,3_1|10180006,4_1</t>
-  </si>
-  <si>
-    <t>10180007,0_2|10180008,1_2|10180009,2_2</t>
-  </si>
-  <si>
-    <t>10180010,0_3</t>
-  </si>
-  <si>
-    <t>10180011,0_4|10180012,1_4</t>
-  </si>
-  <si>
     <t>寒冰王座</t>
   </si>
   <si>
-    <t>10250001,0_0</t>
+    <t>10250011,0_0|10250012,1_0|10250001,2_0</t>
   </si>
   <si>
     <t>10250002,0_1|10250003,1_1|10250004,2_1|10250005,3_1|10250006,4_1</t>
@@ -154,34 +177,28 @@
     <t>10250010,0_3</t>
   </si>
   <si>
-    <t>10250011,0_4|10250012,1_4</t>
-  </si>
-  <si>
     <t>绿巨人</t>
   </si>
   <si>
-    <t>10310001,0_0</t>
-  </si>
-  <si>
-    <t>10310002,0_1|10310003,1_1|10310004,2_1|10310005,3_1</t>
-  </si>
-  <si>
-    <t>10310006,0_2|10310007,1_2|10310008,2_2</t>
-  </si>
-  <si>
-    <t>10310009,0_3|10310010,1_3|10310011,2_3</t>
-  </si>
-  <si>
-    <t>10310012,0_4</t>
-  </si>
-  <si>
-    <t>10310013,0_5|10310014,1_5</t>
+    <t>10310014,0_0|10310015,1_0|10310001,2_0</t>
+  </si>
+  <si>
+    <t>10310002,0_1|10310003,1_1|10310004,2_1|10310005,3_1|10310006,4_1</t>
+  </si>
+  <si>
+    <t>10310007,0_2|10310008,1_2|10310009,2_2</t>
+  </si>
+  <si>
+    <t>10310010,0_3|10310011,1_3|10310012,2_3</t>
+  </si>
+  <si>
+    <t>10310013,0_4</t>
   </si>
   <si>
     <t>雷神</t>
   </si>
   <si>
-    <t>10220001,0_0</t>
+    <t>10220010,0_0|10220011,1_0|10220001,2_0</t>
   </si>
   <si>
     <t>10220002,0_1|10220003,1_1|10220004,2_1|10220005,3_1</t>
@@ -193,13 +210,10 @@
     <t>10220009,0_3</t>
   </si>
   <si>
-    <t>10220010,0_4|10220011,1_4</t>
-  </si>
-  <si>
     <t>杰克船长</t>
   </si>
   <si>
-    <t>10210001,0_0</t>
+    <t>10210014,0_0|10210015,1_0|10210001,2_0</t>
   </si>
   <si>
     <t>10210002,0_1|10210003,1_1|10210004,2_1|10210005,3_1|10210006,4_1</t>
@@ -214,31 +228,10 @@
     <t>10210013,0_4</t>
   </si>
   <si>
-    <t>10210014,0_5|10210015,1_5</t>
-  </si>
-  <si>
-    <t>愤怒的小鸟</t>
-  </si>
-  <si>
-    <t>10390001,0_0</t>
-  </si>
-  <si>
-    <t>10390002,0_1|10390003,1_1|10390004,2_1|10390005,3_1|10390006,4_1</t>
-  </si>
-  <si>
-    <t>10390007,0_2|10390008,1_2|10390009,2_2</t>
-  </si>
-  <si>
-    <t>10390010,0_3</t>
-  </si>
-  <si>
-    <t>10390011,0_4|10390012,1_4</t>
-  </si>
-  <si>
     <t>宙斯vs哈迪斯</t>
   </si>
   <si>
-    <t>10200001,0_0</t>
+    <t>10200011,0_0|10200012,1_0|10200001,2_0</t>
   </si>
   <si>
     <t>10200002,0_1|10200003,1_1|10200004,2_1|10200005,3_1|10200006,4_1</t>
@@ -250,7 +243,22 @@
     <t>10200010,0_3</t>
   </si>
   <si>
-    <t>10200011,0_4|10200012,1_4</t>
+    <t>狼月</t>
+  </si>
+  <si>
+    <t>10150016,0_0|10150017,1_0|10150001,2_0</t>
+  </si>
+  <si>
+    <t>10150002,0_1|10150003,1_1|10150004,2_1|10150005,3_1|10150006,4_1</t>
+  </si>
+  <si>
+    <t>10150007,0_2|10150008,1_2|10150009,2_2</t>
+  </si>
+  <si>
+    <t>10150010,0_3|10150011,1_3|10150012,2_3|10150013,3_3|10150014,4_3</t>
+  </si>
+  <si>
+    <t>10210015,0_4</t>
   </si>
 </sst>
 </file>
@@ -1220,7 +1228,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1304,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>100300</v>
+        <v>103900</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>13</v>
@@ -1324,7 +1332,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>100300</v>
+        <v>103900</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>13</v>
@@ -1344,7 +1352,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="1">
-        <v>100300</v>
+        <v>103900</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>13</v>
@@ -1364,7 +1372,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="1">
-        <v>100300</v>
+        <v>103900</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>13</v>
@@ -1381,16 +1389,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="1">
-        <v>100300</v>
+        <v>102700</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1404,10 +1412,10 @@
         <v>2</v>
       </c>
       <c r="D10" s="1">
-        <v>100700</v>
+        <v>102700</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>20</v>
@@ -1424,12 +1432,12 @@
         <v>2</v>
       </c>
       <c r="D11" s="1">
-        <v>100700</v>
+        <v>102700</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1444,12 +1452,12 @@
         <v>2</v>
       </c>
       <c r="D12" s="1">
-        <v>100700</v>
+        <v>102700</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1461,16 +1469,16 @@
         <v>1</v>
       </c>
       <c r="C13" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="1">
         <v>100700</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1484,10 +1492,10 @@
         <v>3</v>
       </c>
       <c r="D14" s="1">
-        <v>101200</v>
+        <v>100700</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>25</v>
@@ -1504,12 +1512,12 @@
         <v>3</v>
       </c>
       <c r="D15" s="1">
-        <v>101200</v>
+        <v>100700</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1521,16 +1529,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="1">
-        <v>101200</v>
+        <v>101800</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="6" t="s">
         <v>27</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1541,16 +1549,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="1">
-        <v>101200</v>
+        <v>101800</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1561,16 +1569,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="1">
-        <v>101200</v>
+        <v>101800</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1587,7 +1595,7 @@
         <v>101800</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>31</v>
@@ -1601,16 +1609,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="1">
-        <v>101800</v>
+        <v>100300</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1621,16 +1629,16 @@
         <v>1</v>
       </c>
       <c r="C21" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" s="1">
-        <v>101800</v>
+        <v>100300</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1641,16 +1649,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="1">
-        <v>101800</v>
+        <v>100300</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1661,16 +1669,16 @@
         <v>1</v>
       </c>
       <c r="C23" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" s="1">
-        <v>101800</v>
+        <v>100300</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1681,16 +1689,16 @@
         <v>1</v>
       </c>
       <c r="C24" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="1">
-        <v>102500</v>
+        <v>101200</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1701,16 +1709,16 @@
         <v>1</v>
       </c>
       <c r="C25" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="1">
-        <v>102500</v>
+        <v>101200</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1721,16 +1729,16 @@
         <v>1</v>
       </c>
       <c r="C26" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" s="1">
-        <v>102500</v>
+        <v>101200</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1741,16 +1749,16 @@
         <v>1</v>
       </c>
       <c r="C27" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" s="1">
-        <v>102500</v>
+        <v>101200</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1761,16 +1769,16 @@
         <v>1</v>
       </c>
       <c r="C28" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D28" s="1">
         <v>102500</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1781,16 +1789,16 @@
         <v>1</v>
       </c>
       <c r="C29" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" s="1">
-        <v>103100</v>
+        <v>102500</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1801,16 +1809,16 @@
         <v>1</v>
       </c>
       <c r="C30" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30" s="1">
-        <v>103100</v>
+        <v>102500</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>44</v>
+      <c r="F30" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1821,16 +1829,16 @@
         <v>1</v>
       </c>
       <c r="C31" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31" s="1">
-        <v>103100</v>
+        <v>102500</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>45</v>
+      <c r="F31" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1841,16 +1849,16 @@
         <v>1</v>
       </c>
       <c r="C32" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D32" s="1">
         <v>103100</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1861,16 +1869,16 @@
         <v>1</v>
       </c>
       <c r="C33" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D33" s="1">
         <v>103100</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1881,16 +1889,16 @@
         <v>1</v>
       </c>
       <c r="C34" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D34" s="1">
         <v>103100</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1901,16 +1909,16 @@
         <v>1</v>
       </c>
       <c r="C35" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35" s="1">
-        <v>102200</v>
+        <v>103100</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1921,16 +1929,16 @@
         <v>1</v>
       </c>
       <c r="C36" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D36" s="1">
-        <v>102200</v>
+        <v>103100</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1941,16 +1949,16 @@
         <v>1</v>
       </c>
       <c r="C37" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D37" s="1">
         <v>102200</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1961,16 +1969,16 @@
         <v>1</v>
       </c>
       <c r="C38" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D38" s="1">
         <v>102200</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1981,16 +1989,16 @@
         <v>1</v>
       </c>
       <c r="C39" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D39" s="1">
         <v>102200</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2001,16 +2009,16 @@
         <v>1</v>
       </c>
       <c r="C40" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D40" s="1">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2021,16 +2029,16 @@
         <v>1</v>
       </c>
       <c r="C41" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D41" s="1">
         <v>102100</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2041,16 +2049,16 @@
         <v>1</v>
       </c>
       <c r="C42" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D42" s="1">
         <v>102100</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F42" s="6" t="s">
         <v>58</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2061,16 +2069,16 @@
         <v>1</v>
       </c>
       <c r="C43" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D43" s="1">
         <v>102100</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2081,16 +2089,16 @@
         <v>1</v>
       </c>
       <c r="C44" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D44" s="1">
         <v>102100</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2101,16 +2109,16 @@
         <v>1</v>
       </c>
       <c r="C45" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D45" s="1">
         <v>102100</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2121,16 +2129,16 @@
         <v>1</v>
       </c>
       <c r="C46" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D46" s="1">
-        <v>103900</v>
+        <v>102000</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2141,16 +2149,16 @@
         <v>1</v>
       </c>
       <c r="C47" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D47" s="1">
-        <v>103900</v>
+        <v>102000</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2161,16 +2169,16 @@
         <v>1</v>
       </c>
       <c r="C48" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D48" s="1">
-        <v>103900</v>
+        <v>102000</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2181,16 +2189,16 @@
         <v>1</v>
       </c>
       <c r="C49" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D49" s="1">
-        <v>103900</v>
+        <v>102000</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2201,16 +2209,16 @@
         <v>1</v>
       </c>
       <c r="C50" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D50" s="1">
-        <v>103900</v>
+        <v>101500</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2221,16 +2229,16 @@
         <v>1</v>
       </c>
       <c r="C51" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D51" s="1">
-        <v>102000</v>
+        <v>101500</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2241,16 +2249,16 @@
         <v>1</v>
       </c>
       <c r="C52" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D52" s="1">
-        <v>102000</v>
+        <v>101500</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2261,16 +2269,16 @@
         <v>1</v>
       </c>
       <c r="C53" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D53" s="1">
-        <v>102000</v>
+        <v>101500</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2281,36 +2289,16 @@
         <v>1</v>
       </c>
       <c r="C54" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D54" s="1">
-        <v>102000</v>
+        <v>101500</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="1">
-        <v>1051</v>
-      </c>
-      <c r="B55" s="1">
-        <v>1</v>
-      </c>
-      <c r="C55" s="1">
-        <v>10</v>
-      </c>
-      <c r="D55" s="1">
-        <v>102000</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/ResearchInstitute.xlsx
+++ b/hall/resources/sample/ResearchInstitute.xlsx
@@ -1609,7 +1609,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D20" s="1">
         <v>100300</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D21" s="1">
         <v>100300</v>
@@ -1649,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D22" s="1">
         <v>100300</v>
@@ -1669,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D23" s="1">
         <v>100300</v>
@@ -1689,7 +1689,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" s="1">
         <v>101200</v>
@@ -1709,7 +1709,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="1">
         <v>101200</v>
@@ -1729,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="1">
         <v>101200</v>
@@ -1749,7 +1749,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" s="1">
         <v>101200</v>
@@ -1769,7 +1769,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D28" s="1">
         <v>102500</v>
@@ -1789,7 +1789,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D29" s="1">
         <v>102500</v>
@@ -1809,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D30" s="1">
         <v>102500</v>
@@ -1829,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D31" s="1">
         <v>102500</v>
@@ -1849,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="C32" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D32" s="1">
         <v>103100</v>
@@ -1869,7 +1869,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D33" s="1">
         <v>103100</v>
@@ -1889,7 +1889,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D34" s="1">
         <v>103100</v>
@@ -1909,7 +1909,7 @@
         <v>1</v>
       </c>
       <c r="C35" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D35" s="1">
         <v>103100</v>
@@ -1929,7 +1929,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D36" s="1">
         <v>103100</v>
@@ -1949,7 +1949,7 @@
         <v>1</v>
       </c>
       <c r="C37" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D37" s="1">
         <v>102200</v>
@@ -1969,7 +1969,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D38" s="1">
         <v>102200</v>
@@ -1989,7 +1989,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D39" s="1">
         <v>102200</v>
@@ -2009,7 +2009,7 @@
         <v>1</v>
       </c>
       <c r="C40" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D40" s="1">
         <v>102200</v>
@@ -2029,7 +2029,7 @@
         <v>1</v>
       </c>
       <c r="C41" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D41" s="1">
         <v>102100</v>
@@ -2049,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D42" s="1">
         <v>102100</v>
@@ -2069,7 +2069,7 @@
         <v>1</v>
       </c>
       <c r="C43" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D43" s="1">
         <v>102100</v>
@@ -2089,7 +2089,7 @@
         <v>1</v>
       </c>
       <c r="C44" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D44" s="1">
         <v>102100</v>
@@ -2109,7 +2109,7 @@
         <v>1</v>
       </c>
       <c r="C45" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D45" s="1">
         <v>102100</v>
@@ -2129,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="C46" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D46" s="1">
         <v>102000</v>
@@ -2149,7 +2149,7 @@
         <v>1</v>
       </c>
       <c r="C47" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D47" s="1">
         <v>102000</v>
@@ -2169,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="C48" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D48" s="1">
         <v>102000</v>
@@ -2189,7 +2189,7 @@
         <v>1</v>
       </c>
       <c r="C49" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D49" s="1">
         <v>102000</v>
@@ -2209,7 +2209,7 @@
         <v>1</v>
       </c>
       <c r="C50" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D50" s="1">
         <v>101500</v>
@@ -2229,7 +2229,7 @@
         <v>1</v>
       </c>
       <c r="C51" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D51" s="1">
         <v>101500</v>
@@ -2249,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="C52" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D52" s="1">
         <v>101500</v>
@@ -2269,7 +2269,7 @@
         <v>1</v>
       </c>
       <c r="C53" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D53" s="1">
         <v>101500</v>
@@ -2289,7 +2289,7 @@
         <v>1</v>
       </c>
       <c r="C54" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D54" s="1">
         <v>101500</v>
